--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6472-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6472-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAAFB4A2-A75B-421E-8502-417C342A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D022DF6-C2C1-42E4-BDF4-CFEE8305879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E15351DD-6A3D-4D79-8DCF-5FDA81F06EC4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{38F9F5D5-96CC-4246-ABD5-13B2011CE4D9}"/>
   </bookViews>
   <sheets>
     <sheet name="6472-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1601,30 +1601,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3369D44-C964-4224-AB34-092C42EB5D9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89E33A0-9D71-4117-8021-D50CC80B7691}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +1658,7 @@
       <c r="W1" s="36"/>
       <c r="X1" s="28"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
@@ -1694,7 +1694,7 @@
       <c r="W2" s="38"/>
       <c r="X2" s="39"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>2</v>
       </c>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="X3" s="42"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="31"/>
       <c r="B4" s="32"/>
       <c r="C4" s="7"/>
@@ -1814,7 +1814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="43">
         <v>2025</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="45">
         <v>2024</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="47"/>
       <c r="B9" s="48"/>
       <c r="C9" s="18" t="s">
@@ -2134,7 +2134,7 @@
       <c r="W9" s="54"/>
       <c r="X9" s="50"/>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="51" t="s">
         <v>29</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="52"/>
       <c r="B11" s="52"/>
       <c r="C11" s="20" t="s">
@@ -2236,7 +2236,7 @@
       <c r="W11" s="54"/>
       <c r="X11" s="50"/>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="43">
         <v>2023</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="45">
         <v>2022</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="47"/>
       <c r="B18" s="48"/>
       <c r="C18" s="18" t="s">
@@ -2704,7 +2704,7 @@
       <c r="W18" s="54"/>
       <c r="X18" s="50"/>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="51" t="s">
         <v>29</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="52"/>
       <c r="B20" s="52"/>
       <c r="C20" s="20" t="s">
@@ -2806,7 +2806,7 @@
       <c r="W20" s="54"/>
       <c r="X20" s="50"/>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="57">
         <v>2021</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="59"/>
       <c r="B23" s="60"/>
       <c r="C23" s="24" t="s">
@@ -2980,7 +2980,7 @@
       <c r="W23" s="66"/>
       <c r="X23" s="62"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="63" t="s">
         <v>29</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="64"/>
       <c r="B25" s="64"/>
       <c r="C25" s="26" t="s">
@@ -3082,7 +3082,7 @@
       <c r="W25" s="66"/>
       <c r="X25" s="62"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="69">
         <v>2020</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>29</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="57">
         <v>2019</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="59"/>
       <c r="B31" s="60"/>
       <c r="C31" s="24" t="s">
@@ -3476,7 +3476,7 @@
       <c r="W31" s="66"/>
       <c r="X31" s="62"/>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="69">
         <v>2018</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="43">
         <v>2017</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="69">
         <v>2016</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="43">
         <v>2015</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="69">
         <v>2014</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
         <v>56</v>
       </c>
